--- a/exemple-ePrescription/ig/StructureDefinition-fr-cda-administration-de-derives-du-sang.xlsx
+++ b/exemple-ePrescription/ig/StructureDefinition-fr-cda-administration-de-derives-du-sang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T08:51:06+00:00</t>
+    <t>2026-05-06T11:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4701,7 +4701,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>167</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -5105,7 +5105,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>176</v>
       </c>
@@ -5120,13 +5120,13 @@
         <v>62</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5208,7 +5208,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>180</v>
       </c>
@@ -5223,13 +5223,13 @@
         <v>181</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5517,7 +5517,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>194</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
